--- a/Assets/01. Resources/04. Data/GameData.xlsx
+++ b/Assets/01. Resources/04. Data/GameData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HOME\Desktop\Work\DefenseProject\Assets\01. Resources\04. Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zxca0\Desktop\Work\DefenseProject\Assets\01. Resources\04. Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8419BD64-38FC-4396-B4CC-5F961174BA30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2708734-A419-4385-A484-D4CB5E507B64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29280" yWindow="3120" windowWidth="21810" windowHeight="22350" activeTab="4" xr2:uid="{E319F892-31E8-45B4-9486-300862ED73ED}"/>
+    <workbookView xWindow="1845" yWindow="3480" windowWidth="17865" windowHeight="12645" activeTab="4" xr2:uid="{E319F892-31E8-45B4-9486-300862ED73ED}"/>
   </bookViews>
   <sheets>
     <sheet name="Stage" sheetId="1" r:id="rId1"/>
@@ -32,9 +32,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -379,9 +376,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -419,7 +416,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -525,7 +522,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -667,7 +664,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>

--- a/Assets/01. Resources/04. Data/GameData.xlsx
+++ b/Assets/01. Resources/04. Data/GameData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zxca0\Desktop\Work\DefenseProject\Assets\01. Resources\04. Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2708734-A419-4385-A484-D4CB5E507B64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7445B29-602B-4CAB-9FA4-E41684669F99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1845" yWindow="3480" windowWidth="17865" windowHeight="12645" activeTab="4" xr2:uid="{E319F892-31E8-45B4-9486-300862ED73ED}"/>
+    <workbookView xWindow="8070" yWindow="480" windowWidth="17490" windowHeight="13995" firstSheet="1" activeTab="4" xr2:uid="{E319F892-31E8-45B4-9486-300862ED73ED}"/>
   </bookViews>
   <sheets>
     <sheet name="Stage" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="LevelCurve" sheetId="2" r:id="rId3"/>
     <sheet name="Monster" sheetId="3" r:id="rId4"/>
     <sheet name="Item" sheetId="4" r:id="rId5"/>
+    <sheet name="Rule" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1342,4 +1343,14 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D85A509B-40F5-4298-A38A-3C9D2495C706}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Assets/01. Resources/04. Data/GameData.xlsx
+++ b/Assets/01. Resources/04. Data/GameData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zxca0\Desktop\Work\DefenseProject\Assets\01. Resources\04. Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7445B29-602B-4CAB-9FA4-E41684669F99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5B98F82-36BA-4575-B41D-2EEEE91A8EAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8070" yWindow="480" windowWidth="17490" windowHeight="13995" firstSheet="1" activeTab="4" xr2:uid="{E319F892-31E8-45B4-9486-300862ED73ED}"/>
+    <workbookView xWindow="8070" yWindow="480" windowWidth="17490" windowHeight="13995" firstSheet="1" activeTab="1" xr2:uid="{E319F892-31E8-45B4-9486-300862ED73ED}"/>
   </bookViews>
   <sheets>
     <sheet name="Stage" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="69">
   <si>
     <t>Name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -53,14 +53,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Cat</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dog</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Count</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -85,26 +77,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>고양이</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>강아지</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>PrefabKey</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Monster_Cat</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Monster_Dog</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>MoveSpeed</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -306,6 +282,22 @@
   </si>
   <si>
     <t>Instant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Slime</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>박쥐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>슬라임</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -684,18 +676,18 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B2" s="1">
         <v>0</v>
@@ -706,7 +698,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
@@ -717,7 +709,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
@@ -728,7 +720,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B5" s="1">
         <v>3</v>
@@ -739,7 +731,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B6" s="1">
         <v>4</v>
@@ -750,7 +742,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B7" s="1">
         <v>5</v>
@@ -761,7 +753,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B8" s="1">
         <v>6</v>
@@ -772,7 +764,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B9" s="1">
         <v>7</v>
@@ -783,7 +775,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B10" s="1">
         <v>8</v>
@@ -812,21 +804,21 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>3</v>
+        <v>66</v>
       </c>
       <c r="C2" s="1">
         <v>10</v>
@@ -834,10 +826,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>3</v>
+        <v>66</v>
       </c>
       <c r="C3" s="1">
         <v>10</v>
@@ -845,10 +837,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>4</v>
+        <v>65</v>
       </c>
       <c r="C4" s="1">
         <v>10</v>
@@ -856,10 +848,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>3</v>
+        <v>66</v>
       </c>
       <c r="C5" s="1">
         <v>15</v>
@@ -867,10 +859,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>4</v>
+        <v>65</v>
       </c>
       <c r="C6" s="1">
         <v>10</v>
@@ -894,10 +886,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -1002,22 +994,22 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>1</v>
@@ -1028,13 +1020,13 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>65</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="D2" s="1">
         <v>20</v>
@@ -1054,13 +1046,13 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>66</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>12</v>
+        <v>68</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="D3" s="1">
         <v>30</v>
@@ -1102,101 +1094,101 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="F6" s="1">
         <v>7</v>
@@ -1210,19 +1202,19 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="F7" s="1">
         <v>6.6</v>
@@ -1236,19 +1228,19 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="F8" s="1">
         <v>6.1</v>
@@ -1262,19 +1254,19 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>67</v>
-      </c>
       <c r="E9" s="1" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="F9" s="1">
         <v>5.52</v>
@@ -1288,19 +1280,19 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="F10" s="1">
         <v>4.8899999999999997</v>
@@ -1314,19 +1306,19 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="F11" s="1">
         <v>4.53</v>

--- a/Assets/01. Resources/04. Data/GameData.xlsx
+++ b/Assets/01. Resources/04. Data/GameData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zxca0\Desktop\Work\DefenseProject\Assets\01. Resources\04. Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5B98F82-36BA-4575-B41D-2EEEE91A8EAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F4067A7-2230-4C73-8149-A3A75A6C1D9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8070" yWindow="480" windowWidth="17490" windowHeight="13995" firstSheet="1" activeTab="1" xr2:uid="{E319F892-31E8-45B4-9486-300862ED73ED}"/>
+    <workbookView xWindow="1755" yWindow="1620" windowWidth="17490" windowHeight="13995" firstSheet="1" activeTab="3" xr2:uid="{E319F892-31E8-45B4-9486-300862ED73ED}"/>
   </bookViews>
   <sheets>
     <sheet name="Stage" sheetId="1" r:id="rId1"/>
@@ -1032,7 +1032,7 @@
         <v>20</v>
       </c>
       <c r="E2" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F2" s="1">
         <v>2</v>
@@ -1058,7 +1058,7 @@
         <v>30</v>
       </c>
       <c r="E3" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F3" s="1">
         <v>3</v>

--- a/Assets/01. Resources/04. Data/GameData.xlsx
+++ b/Assets/01. Resources/04. Data/GameData.xlsx
@@ -1,24 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zxca0\Desktop\Work\DefenseProject\Assets\01. Resources\04. Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F4067A7-2230-4C73-8149-A3A75A6C1D9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADB3DA6A-BA2F-4475-8F3C-D06662343CBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1755" yWindow="1620" windowWidth="17490" windowHeight="13995" firstSheet="1" activeTab="3" xr2:uid="{E319F892-31E8-45B4-9486-300862ED73ED}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="3" activeTab="5" xr2:uid="{E319F892-31E8-45B4-9486-300862ED73ED}"/>
   </bookViews>
   <sheets>
     <sheet name="Stage" sheetId="1" r:id="rId1"/>
     <sheet name="StageSpawn" sheetId="5" r:id="rId2"/>
     <sheet name="LevelCurve" sheetId="2" r:id="rId3"/>
     <sheet name="Monster" sheetId="3" r:id="rId4"/>
-    <sheet name="Item" sheetId="4" r:id="rId5"/>
-    <sheet name="Rule" sheetId="7" r:id="rId6"/>
+    <sheet name="EnhanceOption" sheetId="8" r:id="rId5"/>
+    <sheet name="EnhanceOptionEffect" sheetId="9" r:id="rId6"/>
+    <sheet name="Localization" sheetId="10" r:id="rId7"/>
+    <sheet name="Item" sheetId="4" r:id="rId8"/>
+    <sheet name="Rule" sheetId="7" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="109">
   <si>
     <t>Name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -298,6 +301,393 @@
   </si>
   <si>
     <t>슬라임</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E_000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"아이템을 1회 제거합니다."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"공격력이 {value} 증가합니다."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"방어막을 즉시 수리합니다."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EffectType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"공격력이 {value0}, 공격속도가 {value1} 증가합니다."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AttackUp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AttackSpeedUp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RemoveItem</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RepairBarrier</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Value</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DescKey</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OPTION_ATTACK_UP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OPTION_ATTACK_SPEED_UP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OPTION_ATTACK_AND_SPEED_UP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OPTION_REMOVE_ITEM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OPTION_REPAIRE_BARRIER</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Key</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>JP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"공격속도가 {value}% 증가합니다."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack increases by {value}.</t>
+  </si>
+  <si>
+    <t>Attack speed increases by {value}%.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack increases by {value0}, and attack speed increases by {value1}%.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Removes 1 item.</t>
+  </si>
+  <si>
+    <t>Instantly repairs the barrier.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>攻</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="MS Mincho"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>撃</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>速度が{value}%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="MS Mincho"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>増</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>加します。</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>攻</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>撃力が</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>{value0}、攻</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>撃速度が</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>{value1}%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>増加します。</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>アイテムを1個削除します。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>シールドを即座に修復します。</t>
+  </si>
+  <si>
+    <r>
+      <t>攻</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>击</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>速度增加{value}%。</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>攻</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>击力增加</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>{value0}，攻</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>击速度增加</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>{value1}%。</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>移除1个道具。</t>
+  </si>
+  <si>
+    <t>立即修复护盾。</t>
+  </si>
+  <si>
+    <r>
+      <t>攻</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>击</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>力增加{value}。</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>攻</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="MS Mincho"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>撃</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>力が{value}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="MS Mincho"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>増</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>加します。</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -305,7 +695,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -320,6 +710,42 @@
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="MS Mincho"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Microsoft JhengHei"/>
+      <family val="2"/>
+      <charset val="136"/>
     </font>
   </fonts>
   <fills count="2">
@@ -344,12 +770,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1078,6 +1507,296 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C1E3122-A954-4950-B941-72CC4BDFF707}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9" style="1"/>
+    <col min="2" max="2" width="32.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
+        <v>1000</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <v>1001</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>1002</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>1003</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <v>1004</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43DBF80E-9D40-48C5-A4C7-FFEB86110EA2}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9" style="1"/>
+    <col min="2" max="2" width="15.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
+        <v>1000</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <v>1001</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C3" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>1002</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C4" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>1002</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C5" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <v>1003</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <v>1004</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{924B26EC-B0F3-4B0D-8EE9-3D77B242B82A}">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="32.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="66.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="44.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="50.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EFDF927-B6D2-44FD-9AE5-8160C7572C38}">
   <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -1337,7 +2056,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D85A509B-40F5-4298-A38A-3C9D2495C706}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>

--- a/Assets/01. Resources/04. Data/GameData.xlsx
+++ b/Assets/01. Resources/04. Data/GameData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zxca0\Desktop\Work\DefenseProject\Assets\01. Resources\04. Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADB3DA6A-BA2F-4475-8F3C-D06662343CBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76646DCC-DFD4-4ED1-8F90-139A3B5DDED1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="3" activeTab="5" xr2:uid="{E319F892-31E8-45B4-9486-300862ED73ED}"/>
+    <workbookView xWindow="1380" yWindow="2115" windowWidth="17490" windowHeight="13995" activeTab="7" xr2:uid="{E319F892-31E8-45B4-9486-300862ED73ED}"/>
   </bookViews>
   <sheets>
     <sheet name="Stage" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="103">
   <si>
     <t>Name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -212,79 +212,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>대지의 지팡이</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>냉기의 지팡이</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>마도서</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>바람의 지팡이</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>불꽃의 지팡이</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Item_CrystalBall</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Item_Scroll</t>
-  </si>
-  <si>
-    <t>Item_Potion</t>
-  </si>
-  <si>
-    <t>Item_Wand</t>
-  </si>
-  <si>
-    <t>Item_IceStaff</t>
-  </si>
-  <si>
-    <t>Item_StoneStaff</t>
-  </si>
-  <si>
-    <t>Item_Grimoire</t>
-  </si>
-  <si>
-    <t>Item_WindStaff</t>
-  </si>
-  <si>
-    <t>Item_FlameStaff</t>
-  </si>
-  <si>
-    <t>Item_QuillPen</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Category</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Buff</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Weapon</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>WeaponType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Projectile</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Instant</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -688,6 +616,62 @@
       </rPr>
       <t>加します。</t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화염 지팡이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>바람 지팡이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>암석 지팡이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>얼음 지팡이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_Weapon_Fire</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_Weapon_Wind</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_Weapon_Grimoire</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_Weapon_Rocks</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_Weapon_Ice</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_Weapon_Water</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_Buff_Potion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_Buff_Scroll</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_Buff_QuillPen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_Buff_CrystalBall</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -778,7 +762,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1247,7 +1231,7 @@
         <v>16</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="C2" s="1">
         <v>10</v>
@@ -1258,7 +1242,7 @@
         <v>25</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="C3" s="1">
         <v>10</v>
@@ -1269,7 +1253,7 @@
         <v>25</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="C4" s="1">
         <v>10</v>
@@ -1280,7 +1264,7 @@
         <v>26</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="C5" s="1">
         <v>15</v>
@@ -1291,7 +1275,7 @@
         <v>26</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="C6" s="1">
         <v>10</v>
@@ -1449,13 +1433,13 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="D2" s="1">
         <v>20</v>
@@ -1475,13 +1459,13 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="D3" s="1">
         <v>30</v>
@@ -1521,10 +1505,10 @@
         <v>8</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -1532,10 +1516,10 @@
         <v>1000</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1543,10 +1527,10 @@
         <v>1001</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -1554,10 +1538,10 @@
         <v>1002</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -1565,10 +1549,10 @@
         <v>1003</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -1576,10 +1560,10 @@
         <v>1004</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -1603,10 +1587,10 @@
         <v>8</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -1614,7 +1598,7 @@
         <v>1000</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="C2" s="1">
         <v>10</v>
@@ -1625,7 +1609,7 @@
         <v>1001</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="C3" s="1">
         <v>11</v>
@@ -1636,7 +1620,7 @@
         <v>1002</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="C4" s="1">
         <v>4</v>
@@ -1647,7 +1631,7 @@
         <v>1002</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="C5" s="1">
         <v>6</v>
@@ -1658,7 +1642,7 @@
         <v>1003</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -1666,7 +1650,7 @@
         <v>1004</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1680,114 +1664,113 @@
   <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="32.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="49.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="66.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="44.375" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="50.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="32.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="66.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="44.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="50.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E2" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D3" t="s">
         <v>83</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="E3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D4" t="s">
         <v>84</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="E4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D5" t="s">
         <v>85</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+      <c r="E5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" t="s">
+        <v>78</v>
+      </c>
+      <c r="D6" t="s">
         <v>86</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>102</v>
+      <c r="E6" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -1798,20 +1781,19 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EFDF927-B6D2-44FD-9AE5-8160C7572C38}">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5" style="1" customWidth="1"/>
     <col min="2" max="2" width="13.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="9" style="1"/>
-    <col min="8" max="8" width="10.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="1"/>
+    <col min="3" max="3" width="22.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="9" style="1"/>
+    <col min="6" max="6" width="10.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -1822,230 +1804,176 @@
         <v>9</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>59</v>
+        <v>7</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>62</v>
+        <v>5</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>29</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C2" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C3" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>31</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C4" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C5" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>33</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>63</v>
+      <c r="C6" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D6" s="1">
+        <v>7</v>
+      </c>
+      <c r="E6" s="1">
+        <v>5</v>
       </c>
       <c r="F6" s="1">
-        <v>7</v>
-      </c>
-      <c r="G6" s="1">
-        <v>5</v>
-      </c>
-      <c r="H6" s="1">
         <v>0.92</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>63</v>
+        <v>92</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D7" s="1">
+        <v>6.6</v>
+      </c>
+      <c r="E7" s="1">
+        <v>7</v>
       </c>
       <c r="F7" s="1">
-        <v>6.6</v>
-      </c>
-      <c r="G7" s="1">
-        <v>7</v>
-      </c>
-      <c r="H7" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>63</v>
+        <v>91</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D8" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="E8" s="1">
+        <v>10</v>
       </c>
       <c r="F8" s="1">
-        <v>6.1</v>
-      </c>
-      <c r="G8" s="1">
-        <v>10</v>
-      </c>
-      <c r="H8" s="1">
         <v>1.08</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>63</v>
+        <v>44</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D9" s="1">
+        <v>5.52</v>
+      </c>
+      <c r="E9" s="1">
+        <v>12</v>
       </c>
       <c r="F9" s="1">
-        <v>5.52</v>
-      </c>
-      <c r="G9" s="1">
-        <v>12</v>
-      </c>
-      <c r="H9" s="1">
         <v>1.17</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>37</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>63</v>
+        <v>90</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D10" s="1">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="E10" s="1">
+        <v>14</v>
       </c>
       <c r="F10" s="1">
-        <v>4.8899999999999997</v>
-      </c>
-      <c r="G10" s="1">
-        <v>14</v>
-      </c>
-      <c r="H10" s="1">
         <v>1.22</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>38</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>64</v>
+        <v>89</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D11" s="1">
+        <v>4.53</v>
+      </c>
+      <c r="E11" s="1">
+        <v>20</v>
       </c>
       <c r="F11" s="1">
-        <v>4.53</v>
-      </c>
-      <c r="G11" s="1">
-        <v>20</v>
-      </c>
-      <c r="H11" s="1">
         <v>1.4</v>
       </c>
     </row>

--- a/Assets/01. Resources/04. Data/GameData.xlsx
+++ b/Assets/01. Resources/04. Data/GameData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zxca0\Desktop\Work\DefenseProject\Assets\01. Resources\04. Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HOME\Desktop\Work\DefenseProject\Assets\01. Resources\04. Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76646DCC-DFD4-4ED1-8F90-139A3B5DDED1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{202B2879-886E-4A30-BC06-B96D726C42E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1380" yWindow="2115" windowWidth="17490" windowHeight="13995" activeTab="7" xr2:uid="{E319F892-31E8-45B4-9486-300862ED73ED}"/>
+    <workbookView xWindow="57495" yWindow="2955" windowWidth="21810" windowHeight="22350" firstSheet="1" activeTab="7" xr2:uid="{E319F892-31E8-45B4-9486-300862ED73ED}"/>
   </bookViews>
   <sheets>
     <sheet name="Stage" sheetId="1" r:id="rId1"/>
@@ -37,12 +37,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="107">
   <si>
     <t>Name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -672,6 +675,22 @@
   </si>
   <si>
     <t>Item_Buff_CrystalBall</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AddSpeed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AddDamage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AddRange</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Critical</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -782,9 +801,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -822,7 +841,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -928,7 +947,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1070,7 +1089,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1781,19 +1800,21 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EFDF927-B6D2-44FD-9AE5-8160C7572C38}">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5" style="1" customWidth="1"/>
     <col min="2" max="2" width="13.75" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="9" style="1"/>
+    <col min="4" max="4" width="9" style="1"/>
+    <col min="5" max="5" width="29.25" style="1" customWidth="1"/>
     <col min="6" max="6" width="10.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="1"/>
+    <col min="7" max="8" width="12.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -1812,8 +1833,20 @@
       <c r="F1" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>29</v>
       </c>
@@ -1823,8 +1856,11 @@
       <c r="C2" s="2" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="I2" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>30</v>
       </c>
@@ -1834,8 +1870,11 @@
       <c r="C3" s="2" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J3" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>31</v>
       </c>
@@ -1845,8 +1884,11 @@
       <c r="C4" s="2" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="H4" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>32</v>
       </c>
@@ -1856,8 +1898,11 @@
       <c r="C5" s="2" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G5" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>33</v>
       </c>
@@ -1868,16 +1913,16 @@
         <v>98</v>
       </c>
       <c r="D6" s="1">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E6" s="1">
-        <v>5</v>
+        <v>5.17</v>
       </c>
       <c r="F6" s="1">
-        <v>0.92</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>34</v>
       </c>
@@ -1888,16 +1933,16 @@
         <v>97</v>
       </c>
       <c r="D7" s="1">
-        <v>6.6</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="E7" s="1">
-        <v>7</v>
+        <v>21.67</v>
       </c>
       <c r="F7" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+        <v>2.04</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>35</v>
       </c>
@@ -1908,16 +1953,16 @@
         <v>96</v>
       </c>
       <c r="D8" s="1">
-        <v>6.1</v>
+        <v>5.6</v>
       </c>
       <c r="E8" s="1">
-        <v>10</v>
+        <v>15.13</v>
       </c>
       <c r="F8" s="1">
-        <v>1.08</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>36</v>
       </c>
@@ -1928,16 +1973,16 @@
         <v>95</v>
       </c>
       <c r="D9" s="1">
-        <v>5.52</v>
+        <v>5.2</v>
       </c>
       <c r="E9" s="1">
-        <v>12</v>
+        <v>18.84</v>
       </c>
       <c r="F9" s="1">
-        <v>1.17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>37</v>
       </c>
@@ -1948,16 +1993,16 @@
         <v>94</v>
       </c>
       <c r="D10" s="1">
-        <v>4.8899999999999997</v>
+        <v>4.2</v>
       </c>
       <c r="E10" s="1">
-        <v>14</v>
+        <v>27.62</v>
       </c>
       <c r="F10" s="1">
-        <v>1.22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+        <v>2.58</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>38</v>
       </c>
@@ -1968,13 +2013,13 @@
         <v>93</v>
       </c>
       <c r="D11" s="1">
-        <v>4.53</v>
+        <v>3.85</v>
       </c>
       <c r="E11" s="1">
-        <v>20</v>
+        <v>44.16</v>
       </c>
       <c r="F11" s="1">
-        <v>1.4</v>
+        <v>2.72</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/01. Resources/04. Data/GameData.xlsx
+++ b/Assets/01. Resources/04. Data/GameData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HOME\Desktop\Work\DefenseProject\Assets\01. Resources\04. Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{202B2879-886E-4A30-BC06-B96D726C42E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FBC7DCF-65A2-4585-B703-3DAEC810EBB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57495" yWindow="2955" windowWidth="21810" windowHeight="22350" firstSheet="1" activeTab="7" xr2:uid="{E319F892-31E8-45B4-9486-300862ED73ED}"/>
+    <workbookView xWindow="32220" yWindow="375" windowWidth="21810" windowHeight="22350" firstSheet="1" activeTab="7" xr2:uid="{E319F892-31E8-45B4-9486-300862ED73ED}"/>
   </bookViews>
   <sheets>
     <sheet name="Stage" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="275">
   <si>
     <t>Name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -239,34 +239,14 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>E_000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>E_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>"아이템을 1회 제거합니다."</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"공격력이 {value} 증가합니다."</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"방어막을 즉시 수리합니다."</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>EffectType</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"공격력이 {value0}, 공격속도가 {value1} 증가합니다."</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>AttackUp</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -299,10 +279,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>OPTION_ATTACK_AND_SPEED_UP</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>OPTION_REMOVE_ITEM</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -339,10 +315,6 @@
   </si>
   <si>
     <t>Attack speed increases by {value}%.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Attack increases by {value0}, and attack speed increases by {value1}%.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -401,64 +373,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>攻</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>撃力が</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>{value0}、攻</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>撃速度が</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>{value1}%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>増加します。</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>アイテムを1個削除します。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -489,54 +403,6 @@
         <scheme val="minor"/>
       </rPr>
       <t>速度增加{value}%。</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>攻</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>击力增加</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>{value0}，攻</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>击速度增加</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>{value1}%。</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -678,10 +544,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>AddSpeed</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>AddDamage</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -692,13 +554,662 @@
   <si>
     <t>Critical</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AddFireInterval</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ExtraDamage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ExtraFireInterval</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ExtraRange</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OPTION_ATTACK_UP_ICE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OPTION_ATTACK_UP_WATER</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OPTION_ATTACK_UP_ROCK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OPTION_ATTACK_UP_WIND</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OPTION_ATTACK_UP_FIRE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OPTION_ATTACK_UP_DARK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OPTION_ATTACK_UP_WATER_ROCK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OPTION_ATTACK_UP_WATER_ICE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OPTION_ATTACK_UP_WATER_WIND</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OPTION_ATTACK_UP_WATER_FIRE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OPTION_ATTACK_UP_WATER_DARK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OPTION_ATTACK_UP_ROCK_ICE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OPTION_ATTACK_UP_ROCK_WIND</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OPTION_ATTACK_UP_ROCK_FIRE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OPTION_ATTACK_UP_ICE_WIND</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OPTION_ATTACK_UP_ICE_FIRE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OPTION_ATTACK_UP_ICE_DARK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OPTION_ATTACK_UP_WIND_FIRE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OPTION_ATTACK_UP_WIND_DARK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OPTION_ATTACK_UP_FIRE_DARK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OPTION_ATTACK_SPEED_WATER</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OPTION_ATTACK_SPEED_ROCK</t>
+  </si>
+  <si>
+    <t>OPTION_ATTACK_SPEED_ICE</t>
+  </si>
+  <si>
+    <t>OPTION_ATTACK_SPEED_WIND</t>
+  </si>
+  <si>
+    <t>OPTION_ATTACK_SPEED_FIRE</t>
+  </si>
+  <si>
+    <t>OPTION_ATTACK_SPEED_DARK</t>
+  </si>
+  <si>
+    <t>OPTION_ATTACK_SPEED_WATER_ROCK</t>
+  </si>
+  <si>
+    <t>OPTION_ATTACK_SPEED_WATER_ICE</t>
+  </si>
+  <si>
+    <t>OPTION_ATTACK_SPEED_WATER_WIND</t>
+  </si>
+  <si>
+    <t>OPTION_ATTACK_SPEED_WATER_FIRE</t>
+  </si>
+  <si>
+    <t>OPTION_ATTACK_SPEED_WATER_DARK</t>
+  </si>
+  <si>
+    <t>OPTION_ATTACK_SPEED_ROCK_ICE</t>
+  </si>
+  <si>
+    <t>OPTION_ATTACK_SPEED_ROCK_WIND</t>
+  </si>
+  <si>
+    <t>OPTION_ATTACK_SPEED_ROCK_FIRE</t>
+  </si>
+  <si>
+    <t>OPTION_ATTACK_SPEED_ICE_WIND</t>
+  </si>
+  <si>
+    <t>OPTION_ATTACK_SPEED_ICE_FIRE</t>
+  </si>
+  <si>
+    <t>OPTION_ATTACK_SPEED_ICE_DARK</t>
+  </si>
+  <si>
+    <t>OPTION_ATTACK_SPEED_WIND_FIRE</t>
+  </si>
+  <si>
+    <t>OPTION_ATTACK_SPEED_WIND_DARK</t>
+  </si>
+  <si>
+    <t>OPTION_ATTACK_SPEED_FIRE_DARK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Water_S</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rock_S</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ice_S</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wind_S</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Water_A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rock_A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ice_A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wind_A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fire_A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dark_A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fire_S</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dark_S</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AttackUp_Water</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AttackUp_Rock</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AttackUp_Ice</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AttackUp_Wind</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AttackUp_Fire</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AttackUp_Dark</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpeedUp_Water</t>
+  </si>
+  <si>
+    <t>SpeedUp_Rock</t>
+  </si>
+  <si>
+    <t>SpeedUp_Ice</t>
+  </si>
+  <si>
+    <t>SpeedUp_Wind</t>
+  </si>
+  <si>
+    <t>SpeedUp_Fire</t>
+  </si>
+  <si>
+    <t>SpeedUp_Dark</t>
+  </si>
+  <si>
+    <t>"물 공격속도가 {value}% 증가합니다."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"암석 공격속도가 {value}% 증가합니다."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"얼음 공격속도가 {value}% 증가합니다."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"바람 공격속도가 {value}% 증가합니다."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"화염 공격속도가 {value}% 증가합니다."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"어둠 공격속도가 {value}% 증가합니다."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>All_A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Repair</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>All_S</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Remove</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"물 공격력이 {value}% 증가합니다."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"암석 공격력이 {value}% 증가합니다."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"얼음 공격력이 {value}% 증가합니다."</t>
+  </si>
+  <si>
+    <t>"바람 공격력이 {value}% 증가합니다."</t>
+  </si>
+  <si>
+    <t>"화염 공격력이 {value}% 증가합니다."</t>
+  </si>
+  <si>
+    <t>"어둠 공격력이 {value}% 증가합니다."</t>
+  </si>
+  <si>
+    <t>"공격력이 {value}% 증가합니다."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"방어막 피해량의 절반을 회복합니다."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ice_Fire_A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ice_Wind_A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ice_Dark_A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fire_Dark_A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wind_Fire_A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wind_Dark_A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rock_Ice_A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rock_Wind_A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rock_Fire_A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OPTION_ATTACK_UP_ROCK_DARK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rock_Dark_A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Water_Rock_A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Water_Wind_A</t>
+  </si>
+  <si>
+    <t>Water_Dark_A</t>
+  </si>
+  <si>
+    <t>Water_Ice_A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Water_Fire_A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Water_Rock_S</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Water_Ice_S</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Water_Wind_S</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Water_Fire_S</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Water_Dark_S</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rock_Ice_S</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rock_Wind_S</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rock_Fire_S</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OPTION_ATTACK_SPEED_ROCK_DARK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rock_Dark_S</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ice_Wind_S</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ice_Fire_S</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ice_Dark_S</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wind_Fire_S</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wind_Dark_S</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fire_Dark_S</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AttackUp_Water_Ice</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AttackUp_Water_Rock</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AttackUp_Water_Wind</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AttackUp_Water_Fire</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AttackUp_Water_Dark</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AttackUp_Rock_Ice</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AttackUp_Rock_Wind</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AttackUp_Rock_Fire</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AttackUp_Rock_Dark</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AttackUp_Ice_Wind</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AttackUp_Ice_Fire</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AttackUp_Ice_Dark</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AttackUp_Wind_Fire</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AttackUp_Wind_Dark</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AttackUp_Fire_Dark</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AttackSpeed_Water_Rock</t>
+  </si>
+  <si>
+    <t>AttackSpeed_Water_Ice</t>
+  </si>
+  <si>
+    <t>AttackSpeed_Water_Wind</t>
+  </si>
+  <si>
+    <t>AttackSpeed_Water_Fire</t>
+  </si>
+  <si>
+    <t>AttackSpeed_Water_Dark</t>
+  </si>
+  <si>
+    <t>AttackSpeed_Rock_Ice</t>
+  </si>
+  <si>
+    <t>AttackSpeed_Rock_Wind</t>
+  </si>
+  <si>
+    <t>AttackSpeed_Rock_Fire</t>
+  </si>
+  <si>
+    <t>AttackSpeed_Rock_Dark</t>
+  </si>
+  <si>
+    <t>AttackSpeed_Ice_Wind</t>
+  </si>
+  <si>
+    <t>AttackSpeed_Ice_Fire</t>
+  </si>
+  <si>
+    <t>AttackSpeed_Ice_Dark</t>
+  </si>
+  <si>
+    <t>AttackSpeed_Wind_Fire</t>
+  </si>
+  <si>
+    <t>AttackSpeed_Wind_Dark</t>
+  </si>
+  <si>
+    <t>AttackSpeed_Fire_Dark</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"물, 암석 공격속도가 {value}% 증가합니다."</t>
+  </si>
+  <si>
+    <t>"물, 얼음 공격속도가 {value}% 증가합니다."</t>
+  </si>
+  <si>
+    <t>"물, 바람 공격속도가 {value}% 증가합니다."</t>
+  </si>
+  <si>
+    <t>"물, 어둠 공격속도가 {value}% 증가합니다."</t>
+  </si>
+  <si>
+    <t>"물, 화염 공격속도가 {value}% 증가합니다."</t>
+  </si>
+  <si>
+    <t>"물, 암석 공격력이 {value}% 증가합니다."</t>
+  </si>
+  <si>
+    <t>"물, 얼음 공격력이 {value}% 증가합니다."</t>
+  </si>
+  <si>
+    <t>"물, 바람 공격력이 {value}% 증가합니다."</t>
+  </si>
+  <si>
+    <t>"물, 화염 공격력이 {value}% 증가합니다."</t>
+  </si>
+  <si>
+    <t>"물, 어둠 공격력이 {value}% 증가합니다."</t>
+  </si>
+  <si>
+    <t>"암석, 얼음 공격속도가 {value}% 증가합니다."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"암석, 바람 공격속도가 {value}% 증가합니다."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"암석, 화염 공격속도가 {value}% 증가합니다."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"암석, 어둠 공격속도가 {value}% 증가합니다."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"얼음, 바람 공격속도가 {value}% 증가합니다."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"얼음, 화염 공격속도가 {value}% 증가합니다."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"얼음, 어둠 공격속도가 {value}% 증가합니다."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"바람, 화염 공격속도가 {value}% 증가합니다."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"바람, 어둠 공격속도가 {value}% 증가합니다."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"화염, 어둠 공격속도가 {value}% 증가합니다."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"화염, 어둠 공격력이 {value}% 증가합니다."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"바람, 화염 공격력이 {value}% 증가합니다."</t>
+  </si>
+  <si>
+    <t>"바람, 어둠 공격력이 {value}% 증가합니다."</t>
+  </si>
+  <si>
+    <t>"얼음, 바람 공격력이 {value}% 증가합니다."</t>
+  </si>
+  <si>
+    <t>"얼음, 화염 공격력이 {value}% 증가합니다."</t>
+  </si>
+  <si>
+    <t>"얼음, 어둠 공격력이 {value}% 증가합니다."</t>
+  </si>
+  <si>
+    <t>"암석, 얼음 공격력이 {value}% 증가합니다."</t>
+  </si>
+  <si>
+    <t>"암석, 바람 공격력이 {value}% 증가합니다."</t>
+  </si>
+  <si>
+    <t>"암석, 화염 공격력이 {value}% 증가합니다."</t>
+  </si>
+  <si>
+    <t>"암석, 어둠 공격력이 {value}% 증가합니다."</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -728,20 +1239,6 @@
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Yu Gothic"/>
-      <family val="2"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Microsoft YaHei"/>
-      <family val="2"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1461,10 +1958,10 @@
         <v>45</v>
       </c>
       <c r="D2" s="1">
-        <v>20</v>
+        <v>2000</v>
       </c>
       <c r="E2" s="1">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="F2" s="1">
         <v>2</v>
@@ -1487,7 +1984,7 @@
         <v>46</v>
       </c>
       <c r="D3" s="1">
-        <v>30</v>
+        <v>3000</v>
       </c>
       <c r="E3" s="1">
         <v>1</v>
@@ -1511,12 +2008,13 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C1E3122-A954-4950-B941-72CC4BDFF707}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C53"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="32.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="9" style="1"/>
+    <col min="2" max="2" width="37.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -1524,7 +2022,7 @@
         <v>8</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>49</v>
@@ -1534,55 +2032,506 @@
       <c r="A2" s="1">
         <v>1000</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>63</v>
+      <c r="B2" s="2" t="s">
+        <v>58</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>50</v>
+        <v>171</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>1001</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>64</v>
+      <c r="B3" s="2" t="s">
+        <v>59</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>50</v>
+        <v>173</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
-        <v>1002</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>65</v>
+        <v>1003</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>60</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>50</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
-        <v>1003</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>66</v>
+        <v>1004</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>61</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="1">
-        <v>1004</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>51</v>
+        <v>172</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <v>1005</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <v>1006</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <v>1007</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <v>1008</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <v>1009</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <v>1010</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
+        <v>1011</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
+        <v>1012</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
+        <v>1013</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
+        <v>1014</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
+        <v>1015</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
+        <v>1016</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
+        <v>1017</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
+        <v>1018</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
+        <v>1019</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
+        <v>1020</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
+        <v>1021</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="1">
+        <v>1022</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="1">
+        <v>1023</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="1">
+        <v>1024</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="1">
+        <v>1025</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="1">
+        <v>1026</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="1">
+        <v>1027</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="1">
+        <v>1028</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="1">
+        <v>1029</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" s="1">
+        <v>1030</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" s="1">
+        <v>1031</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" s="1">
+        <v>1032</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" s="1">
+        <v>1033</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" s="1">
+        <v>1034</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" s="1">
+        <v>1035</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" s="1">
+        <v>1036</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" s="1">
+        <v>1037</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" s="1">
+        <v>1038</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" s="1">
+        <v>1039</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" s="1">
+        <v>1040</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" s="1">
+        <v>1041</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" s="1">
+        <v>1042</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" s="1">
+        <v>1043</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" s="1">
+        <v>1044</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" s="1">
+        <v>1045</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" s="1">
+        <v>1046</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>214</v>
       </c>
     </row>
   </sheetData>
@@ -1593,11 +2542,11 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43DBF80E-9D40-48C5-A4C7-FFEB86110EA2}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C53"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="15.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.75" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1606,10 +2555,10 @@
         <v>8</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -1617,10 +2566,10 @@
         <v>1000</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C2" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1628,48 +2577,500 @@
         <v>1001</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C3" s="1">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" s="1">
-        <v>4</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C5" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="1">
-        <v>1003</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>60</v>
+        <v>153</v>
+      </c>
+      <c r="C7" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <v>1006</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C8" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <v>1007</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C9" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <v>1008</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C10" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <v>1009</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C11" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <v>1010</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="C12" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
+        <v>1011</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C13" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
+        <v>1012</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C14" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
+        <v>1013</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C15" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
+        <v>1014</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C16" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
+        <v>1015</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C17" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
+        <v>1016</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C18" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
+        <v>1017</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C20" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
+        <v>1018</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C21" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
+        <v>1019</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C22" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
+        <v>1020</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C23" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
+        <v>1021</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C24" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="1">
+        <v>1022</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C25" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="1">
+        <v>1023</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="C26" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="1">
+        <v>1024</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="C27" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="1">
+        <v>1025</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="C28" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="1">
+        <v>1026</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C29" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B30" s="2"/>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="1">
+        <v>1027</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="C31" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="1">
+        <v>1028</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="C32" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="1">
+        <v>1029</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="C33" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" s="1">
+        <v>1030</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="C34" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" s="1">
+        <v>1031</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="C35" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" s="1">
+        <v>1032</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C36" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" s="1">
+        <v>1033</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="C37" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" s="1">
+        <v>1034</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C38" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B39" s="2"/>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" s="1">
+        <v>1035</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C40" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" s="1">
+        <v>1036</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="C41" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" s="1">
+        <v>1037</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="C42" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" s="1">
+        <v>1038</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="C43" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" s="1">
+        <v>1039</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C44" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" s="1">
+        <v>1040</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="C45" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B46" s="2"/>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" s="1">
+        <v>1041</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C47" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" s="1">
+        <v>1042</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C48" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" s="1">
+        <v>1043</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="C49" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" s="1">
+        <v>1044</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C50" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B51" s="2"/>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" s="1">
+        <v>1045</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="C52" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" s="1">
+        <v>1046</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="C53" s="1">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1680,7 +3081,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{924B26EC-B0F3-4B0D-8EE9-3D77B242B82A}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32.625" bestFit="1" customWidth="1"/>
@@ -1692,104 +3093,423 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="B1" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C1" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="D1" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="E1" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B2" t="s">
-        <v>53</v>
+        <v>181</v>
       </c>
       <c r="C2" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D2" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="E2" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E4" t="s">
         <v>73</v>
-      </c>
-      <c r="C3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D3" t="s">
-        <v>83</v>
-      </c>
-      <c r="E3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C4" t="s">
-        <v>76</v>
-      </c>
-      <c r="D4" t="s">
-        <v>84</v>
-      </c>
-      <c r="E4" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B5" t="s">
-        <v>52</v>
+        <v>182</v>
       </c>
       <c r="C5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D5" t="s">
         <v>77</v>
       </c>
-      <c r="D5" t="s">
-        <v>85</v>
-      </c>
       <c r="E5" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>67</v>
+      <c r="A6" s="2" t="s">
+        <v>102</v>
       </c>
       <c r="B6" t="s">
-        <v>54</v>
-      </c>
-      <c r="C6" t="s">
-        <v>78</v>
-      </c>
-      <c r="D6" t="s">
-        <v>86</v>
-      </c>
-      <c r="E6" t="s">
-        <v>82</v>
+        <v>175</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B7" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B8" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B9" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B10" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B11" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B12" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B13" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B14" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B15" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B16" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B17" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B18" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B20" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B21" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B22" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B23" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B24" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B25" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B26" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B27" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B28" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B29" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B30" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B31" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B32" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B33" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B34" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B35" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B36" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B37" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B38" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B39" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B40" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B41" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B42" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B43" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B44" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B45" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B46" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B47" t="s">
+        <v>264</v>
       </c>
     </row>
   </sheetData>
@@ -1800,7 +3520,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EFDF927-B6D2-44FD-9AE5-8160C7572C38}">
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5" style="1" customWidth="1"/>
@@ -1808,13 +3528,18 @@
     <col min="3" max="3" width="22.5" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
     <col min="5" max="5" width="29.25" style="1" customWidth="1"/>
-    <col min="6" max="6" width="10.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="12.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="1"/>
+    <col min="6" max="6" width="10.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="12.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -1834,19 +3559,28 @@
         <v>6</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>29</v>
       </c>
@@ -1854,13 +3588,13 @@
         <v>39</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="I2" s="1">
+        <v>93</v>
+      </c>
+      <c r="M2" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>30</v>
       </c>
@@ -1868,13 +3602,13 @@
         <v>40</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="J3" s="1">
+        <v>92</v>
+      </c>
+      <c r="L3" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>31</v>
       </c>
@@ -1882,13 +3616,13 @@
         <v>41</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H4" s="1">
+        <v>91</v>
+      </c>
+      <c r="K4" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>32</v>
       </c>
@@ -1896,13 +3630,13 @@
         <v>42</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="G5" s="1">
+        <v>90</v>
+      </c>
+      <c r="J5" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>33</v>
       </c>
@@ -1910,10 +3644,10 @@
         <v>43</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="D6" s="1">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="E6" s="1">
         <v>5.17</v>
@@ -1921,19 +3655,28 @@
       <c r="F6" s="1">
         <v>0.85</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G6" s="1">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1.22</v>
+      </c>
+      <c r="I6" s="1">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="D7" s="1">
-        <v>4.4000000000000004</v>
+        <v>3.9</v>
       </c>
       <c r="E7" s="1">
         <v>21.67</v>
@@ -1941,19 +3684,28 @@
       <c r="F7" s="1">
         <v>2.04</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G7" s="1">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="H7" s="1">
+        <v>1.22</v>
+      </c>
+      <c r="I7" s="1">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="D8" s="1">
-        <v>5.6</v>
+        <v>3</v>
       </c>
       <c r="E8" s="1">
         <v>15.13</v>
@@ -1961,8 +3713,17 @@
       <c r="F8" s="1">
         <v>1.4</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G8" s="1">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="H8" s="1">
+        <v>1.22</v>
+      </c>
+      <c r="I8" s="1">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>36</v>
       </c>
@@ -1970,10 +3731,10 @@
         <v>44</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="D9" s="1">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="E9" s="1">
         <v>18.84</v>
@@ -1981,19 +3742,28 @@
       <c r="F9" s="1">
         <v>1.67</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G9" s="1">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="H9" s="1">
+        <v>1.22</v>
+      </c>
+      <c r="I9" s="1">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>37</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="D10" s="1">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="E10" s="1">
         <v>27.62</v>
@@ -2001,25 +3771,43 @@
       <c r="F10" s="1">
         <v>2.58</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G10" s="1">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="H10" s="1">
+        <v>1.22</v>
+      </c>
+      <c r="I10" s="1">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>38</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="D11" s="1">
-        <v>3.85</v>
+        <v>3.35</v>
       </c>
       <c r="E11" s="1">
         <v>44.16</v>
       </c>
       <c r="F11" s="1">
         <v>2.72</v>
+      </c>
+      <c r="G11" s="1">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="H11" s="1">
+        <v>1.22</v>
+      </c>
+      <c r="I11" s="1">
+        <v>1.04</v>
       </c>
     </row>
   </sheetData>
